--- a/data/경기도/고양시.xlsx
+++ b/data/경기도/고양시.xlsx
@@ -3,35 +3,35 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="13910" windowHeight="4690" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="13910" windowHeight="4690" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="입력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="행신도서관" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="화정어린이도서관" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="화정어린이도서관" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="행신도서관" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="한뫼도서관" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="아람누리도서관" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="신원도서관" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="화정도서관" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="식사도서관" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="덕이도서관" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="마두도서관" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="삼송도서관" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="대덕도서관" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="화전도서관" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="행신어린이도서관" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="풍동도서관" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="가좌도서관" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="마두도서관" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="덕이도서관" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="별꿈도서관" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="가좌도서관" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="대덕도서관" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="화전도서관" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="행신어린이도서관" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="풍동도서관" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="높빛도서관" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="모당공원도서관" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="대화도서관" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="별꿈도서관" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="내유도서관" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="일산도서관" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="관산도서관" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="사리현도서관" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="주엽어린이도서관" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="마상공원도서관" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="삼송도서관" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="주엽어린이도서관" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="관산도서관" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="사리현도서관" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="일산도서관" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="대화도서관" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="마상공원도서관" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="내유도서관" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="온라인(홈페이지,리브로피아)도서관" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
@@ -479,14 +479,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,14 +519,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -534,7 +535,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>덕이종합자료실</t>
         </is>
       </c>
     </row>
@@ -546,9 +547,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>관내열람 843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -556,21 +558,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>마두북카페</t>
+          <t>덕이종합자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=3</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -578,7 +581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>덕이종합자료실</t>
         </is>
       </c>
     </row>
@@ -590,9 +593,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관내열람 843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -600,51 +604,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>마두북카페</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843.62-이38파-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>마두종합자료실2(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>843.62-이38파-2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>덕이종합자료실</t>
         </is>
       </c>
     </row>
@@ -659,13 +619,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -704,17 +664,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-2=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>[별꿈]자료실</t>
         </is>
       </c>
     </row>
@@ -726,9 +687,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -736,7 +698,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>[별꿈]자료실</t>
         </is>
       </c>
     </row>
@@ -748,9 +710,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -758,7 +721,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>[별꿈]자료실</t>
         </is>
       </c>
     </row>
@@ -770,127 +733,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843-이38파-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>삼송종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>843-이38파-2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>삼송종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>パチンコ. 上</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>M 843-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ミン.ジン.リ- 著 ; 池田眞紀子 譯</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>삼송종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>パチンコ. 下</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>M 843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ミン.ジン.リ- 著 ; 池田眞紀子 譯</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>삼송종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pachinko : a novel</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>W 843-L485p</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>by Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>삼송종합자료실</t>
+          <t>[별꿈]자료실</t>
         </is>
       </c>
     </row>
@@ -905,13 +759,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -945,44 +799,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2=2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 [지음] ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대덕작은자료실</t>
+          <t>&lt;가좌&gt;종합자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ2-1=2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>대덕작은자료실</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ2-2=3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>이민진 [지음] ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ2-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ2-1=3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ2-2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>이민진 [지음] ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>&lt;가좌&gt;종합자료실</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1031,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1052,21 +1047,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>화전작은자료실</t>
+          <t>대덕작은자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
+          <t>843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1074,7 +1070,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>화전작은자료실</t>
+          <t>대덕작은자료실</t>
         </is>
       </c>
     </row>
@@ -1084,6 +1080,100 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>화전작은자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>화전작은자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1137,6 +1227,7 @@
           <t>부모 843.62-이38ㅍ-2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1159,6 +1250,7 @@
           <t>부모 843.62-이38ㅍ-1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1175,7 +1267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1229,6 +1321,7 @@
           <t>843.62-이38ㅍ2-1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1251,6 +1344,7 @@
           <t>843.62-이38ㅍ2-2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1265,14 +1359,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-1=2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1287,14 +1382,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2=2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1317,6 +1413,7 @@
           <t>W 843-L485p</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -1339,6 +1436,7 @@
           <t>W 843-L479p</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -1347,230 +1445,6 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>풍동종합자료실2(2층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1=2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2=3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1=3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
         </is>
       </c>
     </row>
@@ -1630,9 +1504,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1647,14 +1522,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2=2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1674,9 +1550,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1691,14 +1568,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
+          <t>843-이38ㅍ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1713,14 +1591,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843-이38ㅍ</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-1=2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1791,6 +1670,7 @@
           <t>843.6-이38ㅍ-1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1813,6 +1693,7 @@
           <t>843.6-이38ㅍ-2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -1830,6 +1711,846 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-2=2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>843-이38파-2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>843-이38파-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>パチンコ. 上</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M 843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ミン.ジン.リ- 著 ; 池田眞紀子 譯</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>パチンコ. 下</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M 843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ミン.ジン.リ- 著 ; 池田眞紀子 譯</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pachinko : a novel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>W 843-L485p</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>by Min Jin Lee</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코. 1 : 이민진 장편소설.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>부모 843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>화정어린이책사랑(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코. 2 : 이민진 장편소설.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>부모 843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>화정어린이책사랑(2층)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>부모 843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>주엽보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>관산작은자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>관산작은자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>슬픔의 밑바닥에서 고양이가 가르쳐준 소중한 것</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>833.6-다878ㅅ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>다키모리 고토 지음 ; 손지상 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>관산작은자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>사리현작은자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>사리현작은자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[일산]종합자료실1(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[일산]종합자료실1(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-2=2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[일산]종합자료실1(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[일산]종합자료실1(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pachinko</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W 843-L485p</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>by Min Jin Lee</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[일산]국외서-종합자료실2(3층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pachinko</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W 843-L485p</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Min Jin Lee</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[일산]국외서-종합자료실2(3층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[중국]柏靑哥</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>다문화 843-이38ㅂ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>李敏金 著 ; 류勇軍 譯</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[일산]국외서-어린이자료실(1층)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1880,12 +2601,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1902,12 +2624,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=3</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2=2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1919,17 +2642,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843-이38파</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1941,17 +2665,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=4</t>
-        </is>
-      </c>
+          <t>843-이38파</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1971,6 +2696,7 @@
           <t>843.62-이38ㅍ2-1=2</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -1993,6 +2719,7 @@
           <t>843.62-이38ㅍ2-1</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -2015,6 +2742,7 @@
           <t>W 843-L485p</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -2031,20 +2759,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2077,154 +2805,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
+          <t>843.6-이38ㅍ2-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>마상공원작은자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.6-이38ㅍ2-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>행신종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843.62-이38파-2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>행신종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843.62-이38파-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>행신종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>행신종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>파친코 구슬</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>863-뒤52ㅍ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>행신종합자료실</t>
+          <t>마상공원작은자료실</t>
         </is>
       </c>
     </row>
@@ -2233,143 +2853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[별꿈]자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[별꿈]자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[별꿈]자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[별꿈]자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2423,6 +2907,7 @@
           <t>843.6-이38ㅍ-1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2445,6 +2930,7 @@
           <t>843.6-이38ㅍ-2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -2453,576 +2939,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>내유작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pachinko</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>W 843-L485p</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>by Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[일산]국외서-종합자료실2(3층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[중국]柏靑哥</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>다문화 843-이38ㅂ</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>李敏金 著 ; 류勇軍 譯</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[일산]국외서-어린이자료실(1층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pachinko</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>W 843-L485p</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[일산]국외서-종합자료실2(3층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>관산작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>관산작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>슬픔의 밑바닥에서 고양이가 가르쳐준 소중한 것</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>833.6-다878ㅅ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>다키모리 고토 지음 ; 손지상 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>관산작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>사리현작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>사리현작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>부모 843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>주엽보물단지(1층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>마상공원작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>마상공원작은자료실</t>
         </is>
       </c>
     </row>
@@ -3085,11 +3001,13 @@
           <t>전자책 843-이38ㅍ-1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3102,11 +3020,13 @@
           <t>전자책 843-이38ㅍ-1=2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3119,28 +3039,32 @@
           <t>전자책 843-이38ㅍ-2=2</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
+          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>전자책 843-이38ㅍ-1=4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3150,65 +3074,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-2=3</t>
-        </is>
-      </c>
+          <t>전자책 843-이38ㅍ-2=4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
+          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-1=3</t>
-        </is>
-      </c>
+          <t>전자책 843-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
+          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-1=4</t>
-        </is>
-      </c>
+          <t>전자책 843-이38ㅍ-2=3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
+          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-2=4</t>
-        </is>
-      </c>
+          <t>전자책 843-이38ㅍ-1=3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3221,11 +3153,13 @@
           <t>전자책 843-이38ㅍ-2=5</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3238,11 +3172,13 @@
           <t>전자책 843-이38ㅍ-1=5</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3255,11 +3191,13 @@
           <t>전자책 863-뒤52ㅍ=2</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3272,11 +3210,13 @@
           <t>전자책 863-뒤52ㅍ</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3289,14 +3229,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3329,22 +3269,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
+          <t>파친코. 2 : 이민진 장편소설.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>부모 843-이38ㅍ-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>화정어린이책사랑(2층)</t>
+          <t>행신종합자료실</t>
         </is>
       </c>
     </row>
@@ -3356,17 +3297,133 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>부모 843-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>화정어린이책사랑(2층)</t>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코. 1 : 이민진 장편소설.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코. 2 : 이민진 장편소설.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>843.62-이38파-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파친코. 1 : 이민진 장편소설.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>파친코. 1 : 이민진 장편소설.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>843.62-이38파-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>파친코 구슬</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>863-뒤52ㅍ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
         </is>
       </c>
     </row>
@@ -3429,6 +3486,7 @@
           <t>863-뒤52ㅍ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -3451,6 +3509,7 @@
           <t>843.62-이38ㅍ-1</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3465,14 +3524,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3487,14 +3547,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3517,6 +3578,7 @@
           <t>843.62-이38ㅍ-2=2</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3539,6 +3601,7 @@
           <t>W 843-L485pa</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -3609,6 +3672,7 @@
           <t>863-뒤52ㅍ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -3623,14 +3687,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1=3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -3645,14 +3710,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=3</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -3667,14 +3733,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -3697,6 +3764,7 @@
           <t>843.62-이38ㅍ-2=2</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -3711,17 +3779,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=3</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>이민진 지음 ; 이미정 옮김</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3738,9 +3807,10 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3760,9 +3830,10 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3777,17 +3848,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=3</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>이민진 지음 ; 신승미 옮김</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3799,14 +3871,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3826,9 +3899,10 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3851,6 +3925,7 @@
           <t>N 813.6-L479p-2</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>ミン・ジン・リー 著 ; 池田真紀子 [訳]</t>
@@ -3873,6 +3948,7 @@
           <t>N 813.6-L479p-1</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>ミン・ジン・リー 著 ; 池田真紀子 [訳]</t>
@@ -3943,6 +4019,7 @@
           <t>863-뒤52ㅍ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -3965,6 +4042,7 @@
           <t>843.62-이38ㅍ2-2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -3987,6 +4065,7 @@
           <t>843.62-이38ㅍ2-1</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4057,6 +4136,7 @@
           <t>863-뒤52ㅍ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -4079,6 +4159,7 @@
           <t>843.62-이38ㅍ-2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4101,6 +4182,7 @@
           <t>843.62-이38ㅍ-1</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4123,6 +4205,7 @@
           <t>843.62-이38파-2</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4145,6 +4228,7 @@
           <t>843.62-이38파-1</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4167,6 +4251,7 @@
           <t>W 843-L485p</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Min Jin Lee</t>
@@ -4237,6 +4322,7 @@
           <t>863-뒤52ㅍ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
@@ -4259,6 +4345,7 @@
           <t>843.62-이38파-2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4273,14 +4360,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4295,14 +4383,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ2-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4325,6 +4414,7 @@
           <t>843.62-이38ㅍ-2</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4347,6 +4437,7 @@
           <t>843.62-이38파-1</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>이민진 지음 ; 신승미 옮김</t>
@@ -4369,6 +4460,7 @@
           <t>중국 843-이38ㅂ</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>[美]李敏金 著 ; 刘勇军 译</t>
@@ -4391,6 +4483,7 @@
           <t>W 843-L485p</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -4413,6 +4506,7 @@
           <t>W 843-L485p=2</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>by Min Jin Lee</t>
@@ -4435,14 +4529,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4475,14 +4569,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>파친코 : 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4490,7 +4585,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>마두종합자료실2(2층)</t>
         </is>
       </c>
     </row>
@@ -4502,9 +4597,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
+          <t>관내열람 843.62-이38ㅍ-1=2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4512,21 +4608,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>마두북카페</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>파친코 : 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
+          <t>843.62-이38ㅍ-2=3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4534,7 +4631,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>마두종합자료실2(2층)</t>
         </is>
       </c>
     </row>
@@ -4546,9 +4643,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
+          <t>관내열람 843.62-이38ㅍ-2=2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진 지음 ; 이미정 옮김</t>
@@ -4556,7 +4654,53 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>마두북카페</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>843.62-이38파-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>마두종합자료실2(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>파친코 : 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>843.62-이38파-2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>이민진 지음 ; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>마두종합자료실2(2층)</t>
         </is>
       </c>
     </row>

--- a/data/경기도/고양시.xlsx
+++ b/data/경기도/고양시.xlsx
@@ -3,36 +3,25 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="13910" windowHeight="4690" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="13910" windowHeight="4690" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="입력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="화정어린이도서관" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="행신도서관" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="한뫼도서관" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="아람누리도서관" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="신원도서관" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="화정도서관" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="식사도서관" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="아람누리도서관" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="식사도서관" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="풍동도서관" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="화정도서관" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="화정어린이도서관" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="행신어린이도서관" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="대화도서관" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="마두도서관" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="덕이도서관" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="별꿈도서관" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="주엽어린이도서관" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="삼송도서관" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="가좌도서관" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="대덕도서관" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="화전도서관" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="행신어린이도서관" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="풍동도서관" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="높빛도서관" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="모당공원도서관" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="삼송도서관" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="주엽어린이도서관" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="관산도서관" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="사리현도서관" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="일산도서관" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="대화도서관" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="마상공원도서관" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="내유도서관" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="온라인(홈페이지,리브로피아)도서관" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="일산도서관" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="덕이도서관" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="행신도서관" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="한뫼도서관" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -463,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코</t>
+          <t>the chronicles of Narnia</t>
         </is>
       </c>
     </row>
@@ -479,14 +468,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,92 +508,230 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA Prince Caspian : Caspian's Army</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>외국 843-C525c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>adapted by Sadie Chesterfield ; illustrated by Justin Sweet</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>주엽세계어린이도서실(2층)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)last battle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
+          <t>외국 843-L677c-7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>주엽세계어린이도서실(2층)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)silver chair</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
+          <t>외국 843-L677c-6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>주엽세계어린이도서실(2층)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)magician's nephew</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=2</t>
+          <t>외국 843-L677c-1=2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>덕이종합자료실</t>
+          <t>주엽세계어린이도서실(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prince Caspian</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>외국 843-L677c-4=2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>주엽세계어린이도서실(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(THE)horse and his boy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>외국 843-L677c-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>주엽세계어린이도서실(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(THE)magician's nephew</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>외국 843-L677c-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>주엽세계어린이도서실(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(THE)voyage OF THE dawn treader</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>외국 843-L677c-5=2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>주엽세계어린이도서실(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>(THE)lion, THE witch and THE wardrobe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>외국 843-L677c-2=2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>주엽세계어린이도서실(2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>나니아 연대기 : 사자, 마녀 그리고 옷장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>그림 843-루69ㄴ=2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C.S. 루이스 원작 ; 김민선 옮김</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>주엽보물단지(1층)</t>
         </is>
       </c>
     </row>
@@ -619,13 +746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="57" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -659,92 +786,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE) silver chair</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2</t>
+          <t>JW 843-L677c-6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[별꿈]자료실</t>
+          <t>삼송어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE) last battle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>JW 843-L677c-7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[별꿈]자료실</t>
+          <t>삼송어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE) horse and his boy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
+          <t>JW 843-L677c-3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[별꿈]자료실</t>
+          <t>삼송어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE) magician's nephew</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1</t>
+          <t>JW 843-L677c-1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[별꿈]자료실</t>
+          <t>삼송어린이자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prince caspian</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JW 843-L677c-4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>삼송어린이자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(THE) voyage OF THE dawn treader</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JW 843-L677c-5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>삼송어린이자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(THE) lion, THE witch and THE wardrobe</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JW 843-L677c-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>삼송어린이자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>나니아 연대기</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>843-루68ㄴ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C. S. 루이스 글 ; 폴린 베인즈 그림 ; 햇살과나무꾼 옮김</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>삼송종합자료실</t>
         </is>
       </c>
     </row>
@@ -759,14 +978,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -799,184 +1018,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)Last Battle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2=2</t>
+          <t>JW 843-L673c-7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)Silver chair</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1=2</t>
+          <t>JW 843-L673c-6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)Magician's nephew</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>JW 843-L673c-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)Horse and his boys</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
+          <t>JW 843-L673c-3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)Voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2=3</t>
+          <t>JW 843-L673c-5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)Lion, THE witch and THE wardrobe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1</t>
+          <t>JW 843-L673c-2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)Prince Caspian : THE return to NARNIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1=3</t>
+          <t>JW 843-L673c-4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&lt;가좌&gt;종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>이민진 [지음] ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>&lt;가좌&gt;종합자료실</t>
+          <t>&lt;가좌&gt;어린이자료실</t>
         </is>
       </c>
     </row>
@@ -991,14 +1187,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1031,46 +1227,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)voyage OF THE Dawn Treader</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1</t>
+          <t>JW 843-L673c-5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대덕작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>대덕작은자료실</t>
+          <t>[일산]국외서-어린이자료실(1층)</t>
         </is>
       </c>
     </row>
@@ -1085,14 +1258,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="107" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="63" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1125,46 +1298,253 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)last battle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-2</t>
+          <t>W 843-L673c-7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>화전작은자료실</t>
+          <t>덕이종합자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)silver chair</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1</t>
+          <t>W 843-L673c-6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>화전작은자료실</t>
+          <t>덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prince caspian</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>W 843-L673c-4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(THE)horse and his boy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>W 843-L673c-3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(THE)magician＇s nephew</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W 843-L673c-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(THE)voyage OF THE dawn treader</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W 843-L673c-5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(THE)lion, THE witch and THE wardrobe</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>W 843-L673c-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(인도네시아)(THE) CHRONICLES OF NARNIA : Petualangan dawn treader</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>다문화 843-루68ㅋ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>berdasarkan buku C.S. Lewis ; diadaptasi oleh Coralie Noakes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>덕이다문화자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>나니아 연대기</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>아동 843-루68나=2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C. S. 루이스 글 ; 폴린 베인즈 그림 ; 햇살과나무꾼 옮김</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>덕이어린이자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 = CHRONICLES OF NARNIA : 새벽 출정호의 항해 : THE voyage OF THE dawn treader</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D 688-나198-1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>마이클 앱티드 감독</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DVD-덕이종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 = CHRONICLES OF NARNIA : 사자, 마녀 그리고 옷장 : THE lion, THE witch and THE wardrobe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D 688-나198-2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>앤드류 아담슨 감독</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DVD-덕이종합자료실</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1559,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1219,46 +1599,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)Last battle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>부모 843.62-이38ㅍ-2</t>
+          <t>W 843.62-L677c-7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C. S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>행신어린이책사랑(2층)</t>
+          <t>행신종합자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)Silver chair</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>부모 843.62-이38ㅍ-1</t>
+          <t>W 843.62-L677c-6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C. S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>행신어린이책사랑(2층)</t>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(THE)Magician's nephew</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>W 843.62-L677c-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C. S. Lewis by ; Pauline Baynes illustrated by</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(THE)Horse and his boy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>W 843.62-L677c-3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C. S. Lewis by ; Pauline Baynes illustrated by</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(THE)Lion, THE witch and THE wardrobe</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W 843.62-L677c-2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C. S. Lewis by ; Pauline Baynes illustrated by</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 = (THE)CHRONICLES OF NARNIA : Prince Caspian. 2:, 캐스피언 왕자</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D 688-나219-2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>앤드류 아담슨 감독</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>행신디지털자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Prince caspian : THE return to NARNIA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>W 843-L676c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C S Lewis by ; Pauline Baynes illustrated by</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>행신종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 : 사자, 마녀 그리고 옷장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D 688-나219</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>앤드류 아담슨 감독</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>행신디지털자료실</t>
         </is>
       </c>
     </row>
@@ -1273,456 +1791,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>풍동종합자료실1(3층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>풍동종합자료실1(3층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1=2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>풍동종합자료실1(3층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>풍동종합자료실1(3층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pachinko</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>W 843-L485p</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>by Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>풍동종합자료실2(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pachinko</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>W 843-L479p</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>by Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>풍동종합자료실2(2층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[높빛]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[높빛]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[높빛]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[높빛]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1=2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[높빛]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>모당공원작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>모당공원작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="83" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1756,207 +1831,207 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>DVD 나니아 연대기 = The chronicles of Narnia : 캐스피언 왕자 : Prince Caspian. :</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1=2</t>
+          <t>부록있음(Special Features DVD 1매)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>앤드류 아담슨 감독</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼디지털자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)last battle. Book 7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-2</t>
+          <t>W 843-L673c-7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)silver chair. Book 6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-2=2</t>
+          <t>W 843-L673c-6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>Prince caspian. Book 4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843-이38ㅍ-1</t>
+          <t>W 843-L673c-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)Horse and his boy. Book 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843-이38파-2</t>
+          <t>W 843-L673c-3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)Magician's nephew. Book 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843-이38파-1</t>
+          <t>W 843-L673c-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>パチンコ. 上</t>
+          <t>(THE)Voyage OF THE dawn treader. Book 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M 843-이38ㅍ-1</t>
+          <t>W 843-L673c-5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ミン.ジン.リ- 著 ; 池田眞紀子 譯</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>パチンコ. 下</t>
+          <t>(THE)Lion, THE witch and THE wardrobe. Book 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M 843-이38ㅍ-2</t>
+          <t>W 843-L673c-2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ミン.ジン.リ- 著 ; 池田眞紀子 譯</t>
+          <t>by C. S. Lewis, illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼종합자료실</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pachinko : a novel</t>
+          <t>DVD 나니아 연대기 : 사자, 마녀 그리고 옷장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>W 843-L485p</t>
+          <t>D 688-나219-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>by Min Jin Lee</t>
+          <t>앤드류 아담슨 감독</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>삼송종합자료실</t>
+          <t>한뫼디지털자료실</t>
         </is>
       </c>
     </row>
@@ -1971,14 +2046,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="83" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2011,1212 +2086,232 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>부모 843-이38ㅍ-1</t>
+          <t>W 781.542-G823c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>Harry Gregson-Williams</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>화정어린이책사랑(2층)</t>
+          <t>아람예술자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA. 2:, THE lion, THE witch and THE wardrobe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>부모 843-이38ㅍ-2</t>
+          <t>YA 823.91-L677c-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>화정어린이책사랑(2층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>부모 843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>주엽보물단지(1층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>관산작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>관산작은자료실</t>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>슬픔의 밑바닥에서 고양이가 가르쳐준 소중한 것</t>
+          <t>(THE)CHRONICLES OF NARNIA. 5:, THE voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>833.6-다878ㅅ</t>
+          <t>YA 823.91-L677c-5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>다키모리 고토 지음 ; 손지상 옮김</t>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>관산작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>사리현작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>사리현작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[일산]종합자료실1(2층)</t>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 6:, THE silver chair</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
+          <t>YA 823.91-L677c-6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[일산]종합자료실1(2층)</t>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pachinko</t>
+          <t>(THE)CHRONICLES OF NARNIA. 7:, THE last battle</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W 843-L485p</t>
+          <t>YA 823.91-L677c-7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>by Min Jin Lee</t>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[일산]국외서-종합자료실2(3층)</t>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pachinko</t>
+          <t>(THE)CHRONICLES OF NARNIA. 4:, Prince caspian</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>W 843-L485p</t>
+          <t>YA 823.91-L677c-4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Min Jin Lee</t>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[일산]국외서-종합자료실2(3층)</t>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[중국]柏靑哥</t>
+          <t>(THE)CHRONICLES OF NARNIA. 4:, Prince caspian</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다문화 843-이38ㅂ</t>
+          <t>부록있음</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>李敏金 著 ; 류勇軍 譯</t>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[일산]국외서-어린이자료실(1층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-2=2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843-이38파</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1=2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pachinko</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>W 843-L485p</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>by Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>대화종합자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ2-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>마상공원작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ2-2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>마상공원작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>내유작은자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>843.6-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>내유작은자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-1=2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-2=2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-1=4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-2=4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>전자책 843-이38ㅍ-2=3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
+          <t>(THE)Lion, THE Witch and THE Wardrobe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-1=3</t>
+          <t>W 823.912-L673l</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>C. S. Lewis ; Pauline Baynes[illustrated by ]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>아람종합자료실</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 2 : 이민진 장편소설</t>
+          <t>(THE)CHRONICLES OF NARNIA. 1:, THE magician's nephew</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-2=5</t>
+          <t>YA 823.91-L677c-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>by C.S. Lewis ; ill. by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[아람]서고(방문 대출 시 1층 통합데스크 문의/ 평일10:00~21:00/ 주말 10:00~17:00))</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>전자책 (전자책)파친코. 1 : 이민진 장편소설</t>
+          <t>That hideous strength : a modern fairy-tale for grown-ups</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>전자책 843-이38ㅍ-1=5</t>
+          <t>W 823.912-L673t</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코 구슬</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>전자책 863-뒤52ㅍ=2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>전자책 (전자책)파친코 구슬</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>전자책 863-뒤52ㅍ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>아람종합자료실</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3229,13 +2324,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3269,161 +2364,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
+          <t>(THE) CHRONICLES OF NARNIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=2</t>
+          <t>W 843-L677c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis ; with illustrations by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA. 2:, THE Lion, THE witch and THE wardrobe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>W 843-L677ch-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA. 5:, THE voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
+          <t>W 843-L677ch-5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코. 2 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA. 7:, THE Last Battle</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38파-2</t>
+          <t>W 843-L677ch-7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA. 6:, THE Silver chair</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
+          <t>W 843-L677ch-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코. 1 : 이민진 장편소설.</t>
+          <t>(THE)CHRONICLES OF NARNIA. 3:, THE Horse and his boy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843.62-이38파-1</t>
+          <t>W 843-L677ch-3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>파친코 구슬</t>
+          <t>(THE)CHRONICLES OF NARNIA. 1:, THE Magician's Nephew</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>863-뒤52ㅍ</t>
+          <t>W 843-L677ch-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>행신종합자료실</t>
+          <t>식사종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(THE)CHRONICLES OF NARNIA. 4:, Prince caspian</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>W 843-L677ch-4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>식사종합자료실</t>
         </is>
       </c>
     </row>
@@ -3438,14 +2556,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="57" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3478,138 +2596,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 구슬</t>
+          <t>(THE)CHRONICLES OF NARNIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>863-뒤52ㅍ</t>
+          <t>W 843-L673c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+          <t>by C. S. Lewis ; ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>한뫼종합자료실</t>
+          <t>풍동종합자료실2(2층)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>나니아 연대기</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
+          <t>아동 843-루68ㄴ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>C. S. 루이스 글 ; 폴린 베인즈 그림 ; 햇살과나무꾼 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>한뫼종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>한뫼종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>한뫼종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>한뫼종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pachinko</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>W 843-L485pa</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>by Min Jin Lee</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>한뫼종합자료실</t>
+          <t>풍동어린이자료실</t>
         </is>
       </c>
     </row>
@@ -3624,14 +2650,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="128" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="79" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3664,299 +2690,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 구슬</t>
+          <t>(THE)CHRONICLES OF NARNIA. 2 : THE lion, THE witch and THE wardrobe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>863-뒤52ㅍ</t>
+          <t>W 843-L676c-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>아람종합자료실</t>
+          <t>[화정]서고(방문 대출 시 통합데스크 문의, 평일 10:00-21:00, 주말 10:00-17:00)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 3 : THE Horse and his boy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=3</t>
+          <t>W 843-L676c-3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>아람종합자료실</t>
+          <t>[화정]서고(방문 대출 시 통합데스크 문의, 평일 10:00-21:00, 주말 10:00-17:00)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 1 : THE Magician's Nephew</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=3</t>
+          <t>W 843-L676c-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis by ; Pauline Baynes illustrated by</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>아람종합자료실</t>
+          <t>[화정]서고(방문 대출 시 통합데스크 문의, 평일 10:00-21:00, 주말 10:00-17:00)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>DVD 나니아 연대기 = The chronicles of Narnia : 새벽출정호의 항해 : The voyage of the Dawn Treader</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>D 688-나198</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>마이클 앱티드 감독</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>아람종합자료실</t>
+          <t>화정책이음2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>DVD 나니아 연대기 = (THE)CHRONICLES OF NARNIA : Prince Caspian.. 2 :, 캐스피언 왕자 CE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=2</t>
+          <t>D 688-나219-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>앤드류 아담슨 감독</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>아람종합자료실</t>
+          <t>화정책이음2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>DVD 나니아 연대기 콜렉터스 에디션 = The Chronicles Of Narnia : The Lion,Teh Witch And The Wardrobe : 사자,마녀 그리고 옷장. :</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
+          <t>부록있음(스페셜 피쳐 DVD 1매)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>앤드류 아담슨[감독]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-2=2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>843.62-이38ㅍ-1=2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>パチンコ. 下</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>N 813.6-L479p-2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ミン・ジン・リー 著 ; 池田真紀子 [訳]</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>パチンコ. 上</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>N 813.6-L479p-1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ミン・ジン・リー 著 ; 池田真紀子 [訳]</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>아람종합자료실</t>
+          <t>화정책이음2</t>
         </is>
       </c>
     </row>
@@ -3971,14 +2836,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="83" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4011,69 +2876,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 구슬</t>
+          <t>(THE)CHRONICLES OF NARNIA. 2 : THE lion, THE witch and THE wardrobe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>863-뒤52ㅍ</t>
+          <t>외국 843.62-L677c-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[신원]보존서고: 방문대출 시 종합자료실 문의/ 평일 10:00~21:00 / 주말 10:00~17:00</t>
+          <t>화정어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 5 : THE voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2</t>
+          <t>외국 843.62-L677c-5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>신원종합자료실</t>
+          <t>화정어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 7 : THE last battle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1</t>
+          <t>외국 843.62-L677c-7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>신원종합자료실</t>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(THE)CHRONICLES OF NARNIA. 1 : THE magician's nephew</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677c-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(THE)CHRONICLES OF NARNIA. 6 : THE silver chair</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677c-6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(THE)CHRONICLES OF NARNIA. 3 : THE horse and his boy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677c-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(THE)CHRONICLES OF NARNIA. 4 : Prince caspian</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677c-4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(THE)last battle. Book 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>(THE)silver chair. Book 6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>(THE)Horse and his boy. Book 3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Prince caspian. Book 4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>(THE)magician's nephew. Book 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>(THE)voyage OF THE dawn treader. Book 5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>(THE)Lion, THE witch and THE wardrobe. Book 2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>외국 843.62-L677ch-2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>화정어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
@@ -4088,14 +3206,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="79" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4128,138 +3246,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 구슬</t>
+          <t>(THE)CHRONICLES OF NARNIA. 2 : THE lion, THE witch and THE wardrobe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>863-뒤52ㅍ</t>
+          <t>JW 843.62-L677c-2=2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[화정]서고(방문 대출 시 통합데스크 문의, 평일 10:00-21:00, 주말 10:00-17:00)</t>
+          <t>행신어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 5 : THE voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>JW 843.62-L677c-5=2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>화정종합자료실1</t>
+          <t>행신어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 6 : THE silver chair</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1</t>
+          <t>JW 843.62-L677c-6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>화정종합자료실1</t>
+          <t>행신어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 4 : Prince caspian</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38파-2</t>
+          <t>JW 843.62-L677c-4=2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>화정종합자료실1</t>
+          <t>행신어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 3 : THE horse and his boy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.62-이38파-1</t>
+          <t>JW 843.62-L677c-3=2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>화정종합자료실1</t>
+          <t>행신어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pachinko</t>
+          <t>(THE)CHRONICLES OF NARNIA. 7 : THE last battle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>W 843-L485p</t>
+          <t>JW 843.62-L677c-7=2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Min Jin Lee</t>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>화정종합자료실1</t>
+          <t>행신어린이보물단지(1층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(THE)CHRONICLES OF NARNIA. 1 : THE magician's nephew</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JW 843.62-L677c-1=2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis, ill. by Pauline Baynes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>행신어린이보물단지(1층)</t>
         </is>
       </c>
     </row>
@@ -4274,13 +3415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -4314,207 +3455,230 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 구슬</t>
+          <t>(THE)CHRONICLES OF NARNIA. 2, (THE)Lion, THE Witch and THE Wardrobe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>863-뒤52ㅍ</t>
+          <t>JW 843-L676c-2=2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>엘리자 수아 뒤사팽 지음 ; 이상해 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 5, (THE)Voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.62-이38파-2</t>
+          <t>JW 843-L676c-5=2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 6, (THE)Silver chair</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-2</t>
+          <t>JW 843-L676c-6=2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 1, (THE)Magician's nephew</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ2-1</t>
+          <t>JW 843-L676c-1=2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 3, (THE)Horse and his boy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2</t>
+          <t>JW 843-L676c-3=2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 7, (THE)Last battle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843.62-이38파-1</t>
+          <t>JW 843-L676c-7=2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>柏青哥</t>
+          <t>(THE)CHRONICLES OF NARNIA. 1, THE Magician's Nephew</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>중국 843-이38ㅂ</t>
+          <t>JW 843-L676c-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[美]李敏金 著 ; 刘勇军 译</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pachinko</t>
+          <t>(THE)CHRONICLES OF NARNIA. 4, Prince caspian</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>W 843-L485p</t>
+          <t>JW 843-L676c-4=2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>by Min Jin Lee</t>
+          <t>by C. S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화어린이자료실</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pachinko : Roman</t>
+          <t>DVD 나니아 연대기 = The chronicles of Narnia : 새벽출정호의 항해 : The voyage of the Dawn Treader</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>W 843-L485p=2</t>
+          <t>D 688-나198ㅇ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>by Min Jin Lee</t>
+          <t>마이클 앱티드 감독</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>식사종합자료실</t>
+          <t>대화디지털자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 = The chronicles of Narnia : 캐스피언 왕자 : Prince Caspian</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D 688-나219-2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>앤드류 아담슨 감독</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>대화디지털자료실</t>
         </is>
       </c>
     </row>
@@ -4529,14 +3693,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4569,138 +3733,253 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 7, THE last battle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-1=2</t>
+          <t>W 843.62-L673c-7=2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>마두종합자료실1(3층)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 1, THE magician's nephew</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>관내열람 843.62-이38ㅍ-1=2</t>
+          <t>W 843.62-L673c-1=2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>마두북카페</t>
+          <t>마두종합자료실1(3층)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 5, THE voyage OF THE dawn treader</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843.62-이38ㅍ-2=3</t>
+          <t>W 843.62-L673c-5=2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>마두종합자료실1(3층)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 6, THE silver chair</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관내열람 843.62-이38ㅍ-2=2</t>
+          <t>W 843.62-L673c-6=2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 이미정 옮김</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>마두북카페</t>
+          <t>마두종합자료실1(3층)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 1</t>
+          <t>(THE)CHRONICLES OF NARNIA. 3, THE horse and his boy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.62-이38파-1</t>
+          <t>W 843.62-L673c-3=2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>마두종합자료실1(3층)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코 : 이민진 장편소설. 2</t>
+          <t>(THE)CHRONICLES OF NARNIA. 4, Prince caspian</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843.62-이38파-2</t>
+          <t>W 843.62-L673c-4=2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진 지음 ; 신승미 옮김</t>
+          <t>C.S. Lewis ; illustrated by Pauline Baynes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>마두종합자료실2(2층)</t>
+          <t>마두종합자료실1(3층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(THE)magician's nephew</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>W 843.62-L673c-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>마두종합자료실1(3층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(THE)voyage OF THE dawn treader</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>W 843.62-L677c-5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>마두종합자료실1(3층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>(THE)lion, THE witch and THE wardrobe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>W 843.62-L673c-2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>by C.S. Lewis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>마두종합자료실1(3층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 = The chronicles of Narnia : 새벽출정호의 항해 : The voyage of the Dawn Treader</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D 688-나198ㅇ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>마이클 앱티드 감독</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>마두책이음 1층(비도서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DVD 나니아 연대기 = The chronicles of Narnia : 캐스피언 왕자 : Prince Caspian</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>부록있음(Special Features DVD 1매)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>앤드류 아담슨 감독</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>마두책이음 1층(비도서)</t>
         </is>
       </c>
     </row>
